--- a/Result/profitability/1709.xlsx
+++ b/Result/profitability/1709.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0.31625</v>
+        <v>0.35875</v>
       </c>
       <c r="N2" t="n">
-        <v>14.9125</v>
+        <v>16.91</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.41</v>
       </c>
       <c r="M3" t="n">
-        <v>0.31625</v>
+        <v>0.39</v>
       </c>
       <c r="N3" t="n">
-        <v>14.40625</v>
+        <v>16.93</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.89</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4075</v>
+        <v>0.45125</v>
       </c>
       <c r="N4" t="n">
-        <v>15.08875</v>
+        <v>16.99</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3150000000000001</v>
+        <v>0.3925</v>
       </c>
       <c r="N5" t="n">
-        <v>12.25625</v>
+        <v>14.855</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.32</v>
+        <v>0.37125</v>
       </c>
       <c r="N6" t="n">
-        <v>12.20625</v>
+        <v>14.635</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.315</v>
+        <v>0.3625</v>
       </c>
       <c r="N7" t="n">
-        <v>12.45875</v>
+        <v>14.3075</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>0.305</v>
+        <v>0.33</v>
       </c>
       <c r="N8" t="n">
-        <v>12.165</v>
+        <v>13.67</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2689</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1819</v>
+      </c>
+      <c r="E75" t="n">
+        <v>870</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>663</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>24.67%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-231</v>
+      </c>
+      <c r="J75" t="n">
+        <v>432</v>
+      </c>
+      <c r="K75" t="n">
+        <v>356</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.56625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3636363636363635</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.5922282341367437</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.769230769230769</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.795336787564767</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
